--- a/Excel/MonsterFestiveConfig.xlsx
+++ b/Excel/MonsterFestiveConfig.xlsx
@@ -30,7 +30,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="75">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
@@ -83,97 +86,106 @@
     <t>节日小鸡</t>
   </si>
   <si>
-    <t>30000</t>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>10000</t>
   </si>
   <si>
     <t>10000000</t>
   </si>
   <si>
+    <t>2002,2007</t>
+  </si>
+  <si>
+    <t>节日小鹿</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>20000000</t>
+  </si>
+  <si>
+    <t>1002,2007</t>
+  </si>
+  <si>
+    <t>节日小花</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>50000000</t>
+  </si>
+  <si>
+    <t>节日骷髅</t>
+  </si>
+  <si>
+    <t>150000</t>
+  </si>
+  <si>
+    <t>75000000</t>
+  </si>
+  <si>
+    <t>节日毒蛇</t>
+  </si>
+  <si>
+    <t>300000</t>
+  </si>
+  <si>
+    <t>200000000</t>
+  </si>
+  <si>
+    <t>1012,2007</t>
+  </si>
+  <si>
+    <t>节日僵尸</t>
+  </si>
+  <si>
+    <t>600000</t>
+  </si>
+  <si>
+    <t>400000000</t>
+  </si>
+  <si>
+    <t>节日恶魔</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>800000000</t>
+  </si>
+  <si>
+    <t>节日蜈蚣</t>
+  </si>
+  <si>
+    <t>2000000</t>
+  </si>
+  <si>
+    <t>1600000000</t>
+  </si>
+  <si>
     <t>1012,2007,1008</t>
   </si>
   <si>
-    <t>节日小鹿</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>20000000</t>
-  </si>
-  <si>
-    <t>2002,2007,1008</t>
-  </si>
-  <si>
-    <t>节日小花</t>
-  </si>
-  <si>
-    <t>70000</t>
-  </si>
-  <si>
-    <t>40000000</t>
-  </si>
-  <si>
-    <t>节日骷髅</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>70000000</t>
-  </si>
-  <si>
-    <t>节日毒蛇</t>
-  </si>
-  <si>
-    <t>120000</t>
-  </si>
-  <si>
-    <t>100000000</t>
-  </si>
-  <si>
-    <t>节日僵尸</t>
-  </si>
-  <si>
-    <t>150000</t>
-  </si>
-  <si>
-    <t>140000000</t>
-  </si>
-  <si>
-    <t>节日恶魔</t>
-  </si>
-  <si>
-    <t>180000</t>
-  </si>
-  <si>
-    <t>210000000</t>
-  </si>
-  <si>
-    <t>节日蜈蚣</t>
-  </si>
-  <si>
-    <t>210000</t>
-  </si>
-  <si>
-    <t>300000000</t>
-  </si>
-  <si>
     <t>节日野猪</t>
   </si>
   <si>
-    <t>250000</t>
-  </si>
-  <si>
-    <t>400000000</t>
+    <t>3000000</t>
+  </si>
+  <si>
+    <t>3000000000</t>
   </si>
   <si>
     <t>节日邪魔</t>
   </si>
   <si>
-    <t>300000</t>
-  </si>
-  <si>
-    <t>500000000</t>
+    <t>4000000</t>
+  </si>
+  <si>
+    <t>6000000000</t>
   </si>
   <si>
     <t>节日红蛛</t>
@@ -206,9 +218,6 @@
     <t>节日冰龙</t>
   </si>
   <si>
-    <t>600000</t>
-  </si>
-  <si>
     <t>900000000</t>
   </si>
   <si>
@@ -224,9 +233,6 @@
     <t>节日巨魔</t>
   </si>
   <si>
-    <t>1000000</t>
-  </si>
-  <si>
     <t>1500000000</t>
   </si>
   <si>
@@ -249,12 +255,6 @@
   </si>
   <si>
     <t>节日骨魔</t>
-  </si>
-  <si>
-    <t>2000000</t>
-  </si>
-  <si>
-    <t>3000000000</t>
   </si>
 </sst>
 </file>
@@ -443,13 +443,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -894,45 +894,41 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1252,234 +1248,292 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="5" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="17" style="5" customWidth="1"/>
-    <col min="7" max="8" width="19.25" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="12" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="33.9166666666667" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="5" max="5" width="11.625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="17" style="6" customWidth="1"/>
+    <col min="7" max="8" width="19.25" style="6" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="12" style="4" customWidth="1"/>
+    <col min="13" max="13" width="9.375" style="4" customWidth="1"/>
+    <col min="14" max="14" width="33.9166666666667" style="4" customWidth="1"/>
+    <col min="15" max="16" width="9" style="4"/>
+    <col min="17" max="17" width="11.625" style="6" customWidth="1"/>
+    <col min="18" max="18" width="17" style="6" customWidth="1"/>
+    <col min="19" max="19" width="19.25" style="6" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="Q1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="Q2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="7" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="R5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:19">
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="11">
         <v>0</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="I6" s="2">
+        <v>100</v>
+      </c>
+      <c r="J6" s="2">
+        <v>100</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M6" s="2">
+        <v>99</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="S6" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C7" s="5">
         <v>2</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:14">
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="10">
-        <v>10</v>
-      </c>
-      <c r="I6" s="16">
-        <v>100</v>
-      </c>
-      <c r="J6" s="16">
-        <v>1800</v>
-      </c>
-      <c r="K6" s="16">
-        <v>1800</v>
-      </c>
-      <c r="L6" s="16">
-        <v>1800</v>
-      </c>
-      <c r="M6" s="16">
-        <v>99</v>
-      </c>
-      <c r="N6" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C7" s="11">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="11">
+        <f t="shared" ref="H7:H15" si="0">H6+20</f>
         <v>20</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="14">
-        <f t="shared" ref="H7:H24" si="0">H6+10</f>
-        <v>20</v>
-      </c>
-      <c r="I7" s="16">
+      <c r="I7" s="2">
         <v>100</v>
       </c>
       <c r="J7" s="2">
@@ -1494,31 +1548,40 @@
       <c r="M7" s="2">
         <v>99</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="N7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="14" t="s">
         <v>23</v>
       </c>
+      <c r="R7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" s="14" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C8" s="11">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C8" s="5">
         <v>3</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="19" t="s">
+      <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="14">
+      <c r="E8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="11">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="I8" s="16">
+        <v>40</v>
+      </c>
+      <c r="I8" s="2">
         <v>100</v>
       </c>
       <c r="J8" s="2">
@@ -1533,31 +1596,40 @@
       <c r="M8" s="2">
         <v>99</v>
       </c>
-      <c r="N8" s="18" t="s">
-        <v>19</v>
+      <c r="N8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C9" s="11">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C9" s="5">
         <v>4</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="19" t="s">
+      <c r="D9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="14">
+      <c r="E9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="11">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="I9" s="16">
+        <v>60</v>
+      </c>
+      <c r="I9" s="2">
         <v>100</v>
       </c>
       <c r="J9" s="2">
@@ -1572,31 +1644,40 @@
       <c r="M9" s="2">
         <v>99</v>
       </c>
-      <c r="N9" s="18" t="s">
-        <v>23</v>
+      <c r="N9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C10" s="11">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C10" s="5">
         <v>5</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="19" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="14">
+      <c r="E10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="11">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="I10" s="16">
+        <v>80</v>
+      </c>
+      <c r="I10" s="2">
         <v>100</v>
       </c>
       <c r="J10" s="2">
@@ -1611,31 +1692,40 @@
       <c r="M10" s="2">
         <v>99</v>
       </c>
-      <c r="N10" s="18" t="s">
-        <v>19</v>
+      <c r="N10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="R10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" s="14" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C11" s="11">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C11" s="5">
         <v>6</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="14">
+      <c r="D11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="11">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="I11" s="16">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
         <v>100</v>
       </c>
       <c r="J11" s="2">
@@ -1650,33 +1740,40 @@
       <c r="M11" s="2">
         <v>99</v>
       </c>
-      <c r="N11" s="18" t="s">
-        <v>19</v>
+      <c r="N11" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="R11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="S11" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="11">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C12" s="5">
         <v>7</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="14">
+      <c r="D12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="11">
         <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="I12" s="16">
+        <v>120</v>
+      </c>
+      <c r="I12" s="2">
         <v>100</v>
       </c>
       <c r="J12" s="2">
@@ -1691,33 +1788,40 @@
       <c r="M12" s="2">
         <v>99</v>
       </c>
-      <c r="N12" s="18" t="s">
-        <v>19</v>
+      <c r="N12" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="R12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="S12" s="14" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="11">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C13" s="5">
         <v>8</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="14">
+      <c r="D13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="11">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="I13" s="16">
+        <v>140</v>
+      </c>
+      <c r="I13" s="2">
         <v>100</v>
       </c>
       <c r="J13" s="2">
@@ -1732,33 +1836,40 @@
       <c r="M13" s="2">
         <v>99</v>
       </c>
-      <c r="N13" s="18" t="s">
-        <v>19</v>
+      <c r="N13" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="R13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S13" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="11">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C14" s="5">
         <v>9</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="14">
+      <c r="D14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="11">
         <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="I14" s="16">
+        <v>160</v>
+      </c>
+      <c r="I14" s="2">
         <v>100</v>
       </c>
       <c r="J14" s="2">
@@ -1773,33 +1884,40 @@
       <c r="M14" s="2">
         <v>99</v>
       </c>
-      <c r="N14" s="18" t="s">
-        <v>19</v>
+      <c r="N14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="R14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="S14" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="11">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:19">
+      <c r="C15" s="5">
         <v>10</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="D15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="11">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="I15" s="16">
+        <v>180</v>
+      </c>
+      <c r="I15" s="2">
         <v>100</v>
       </c>
       <c r="J15" s="2">
@@ -1814,382 +1932,514 @@
       <c r="M15" s="2">
         <v>99</v>
       </c>
-      <c r="N15" s="18" t="s">
+      <c r="N15" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="R15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="S15" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="12">
+        <v>11</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="13">
+        <f t="shared" ref="H7:H24" si="1">H15+10</f>
+        <v>190</v>
+      </c>
+      <c r="I16" s="3">
+        <v>100</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M16" s="3">
+        <v>99</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="R16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="12">
+        <v>12</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="13">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M17" s="3">
+        <v>99</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="R17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="S17" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="12">
+        <v>13</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="13">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M18" s="3">
+        <v>99</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="R18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="S18" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="12">
+        <v>14</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="13">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="I19" s="3">
+        <v>100</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K19" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M19" s="3">
+        <v>99</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="S19" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="12">
+        <v>15</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" s="13">
+        <f t="shared" si="1"/>
+        <v>230</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M20" s="3">
+        <v>99</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="R20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="S20" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="12">
+        <v>16</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="13">
+        <f t="shared" si="1"/>
+        <v>240</v>
+      </c>
+      <c r="I21" s="3">
+        <v>100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M21" s="3">
+        <v>99</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="R21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="S21" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="12">
+        <v>17</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="13">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="I22" s="3">
+        <v>100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M22" s="3">
+        <v>99</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="R22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="S22" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A23" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="12">
+        <v>18</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="13">
+        <f t="shared" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="I23" s="3">
+        <v>100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M23" s="3">
+        <v>99</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="R23" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="S23" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:19">
+      <c r="A24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="12">
         <v>19</v>
       </c>
+      <c r="D24" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="13">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M24" s="3">
+        <v>99</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q24" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="R24" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="S24" s="16" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="11">
-        <v>11</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="14">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="I16" s="16">
-        <v>100</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L16" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M16" s="2">
-        <v>99</v>
-      </c>
-      <c r="N16" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="11">
-        <v>12</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="14">
-        <f t="shared" si="0"/>
-        <v>120</v>
-      </c>
-      <c r="I17" s="16">
-        <v>100</v>
-      </c>
-      <c r="J17" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K17" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L17" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M17" s="2">
-        <v>99</v>
-      </c>
-      <c r="N17" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="11">
-        <v>13</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" s="14">
-        <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-      <c r="I18" s="16">
-        <v>100</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L18" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M18" s="2">
-        <v>99</v>
-      </c>
-      <c r="N18" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="11">
-        <v>14</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" s="14">
-        <f t="shared" si="0"/>
-        <v>140</v>
-      </c>
-      <c r="I19" s="16">
-        <v>100</v>
-      </c>
-      <c r="J19" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L19" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M19" s="2">
-        <v>99</v>
-      </c>
-      <c r="N19" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="11">
-        <v>15</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="14">
-        <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-      <c r="I20" s="16">
-        <v>100</v>
-      </c>
-      <c r="J20" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L20" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M20" s="2">
-        <v>99</v>
-      </c>
-      <c r="N20" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="11">
-        <v>16</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="14">
-        <f t="shared" si="0"/>
-        <v>160</v>
-      </c>
-      <c r="I21" s="16">
-        <v>100</v>
-      </c>
-      <c r="J21" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K21" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L21" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M21" s="2">
-        <v>99</v>
-      </c>
-      <c r="N21" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="11">
-        <v>17</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="H22" s="14">
-        <f t="shared" si="0"/>
-        <v>170</v>
-      </c>
-      <c r="I22" s="16">
-        <v>100</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L22" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M22" s="2">
-        <v>99</v>
-      </c>
-      <c r="N22" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="11">
-        <v>18</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="14">
-        <f t="shared" si="0"/>
-        <v>180</v>
-      </c>
-      <c r="I23" s="16">
-        <v>100</v>
-      </c>
-      <c r="J23" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K23" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L23" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M23" s="2">
-        <v>99</v>
-      </c>
-      <c r="N23" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="11">
-        <v>19</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H24" s="14">
-        <f t="shared" si="0"/>
-        <v>190</v>
-      </c>
-      <c r="I24" s="16">
-        <v>100</v>
-      </c>
-      <c r="J24" s="2">
-        <v>1800</v>
-      </c>
-      <c r="K24" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L24" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M24" s="2">
-        <v>99</v>
-      </c>
-      <c r="N24" s="18" t="s">
-        <v>19</v>
-      </c>
+    <row r="25" customHeight="1" spans="5:19">
+      <c r="E25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="S25" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 N3:N5 D3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5 Q3:S5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterFestiveConfig.xlsx
+++ b/Excel/MonsterFestiveConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
   <si>
     <t>#</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Protect</t>
   </si>
   <si>
-    <t>SkillIdList</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -80,181 +77,124 @@
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
     <t>节日小鸡</t>
   </si>
   <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>节日小鹿</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>节日小花</t>
+  </si>
+  <si>
     <t>20000</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>10000000</t>
-  </si>
-  <si>
-    <t>2002,2007</t>
-  </si>
-  <si>
-    <t>节日小鹿</t>
+    <t>节日骷髅</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>节日毒蛇</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>节日僵尸</t>
   </si>
   <si>
     <t>50000</t>
   </si>
   <si>
-    <t>20000000</t>
-  </si>
-  <si>
-    <t>1002,2007</t>
-  </si>
-  <si>
-    <t>节日小花</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>50000000</t>
-  </si>
-  <si>
-    <t>节日骷髅</t>
-  </si>
-  <si>
-    <t>150000</t>
-  </si>
-  <si>
-    <t>75000000</t>
-  </si>
-  <si>
-    <t>节日毒蛇</t>
+    <t>节日恶魔</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>节日蜈蚣</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>节日野猪</t>
+  </si>
+  <si>
+    <t>130000</t>
+  </si>
+  <si>
+    <t>节日邪魔</t>
+  </si>
+  <si>
+    <t>170000</t>
+  </si>
+  <si>
+    <t>节日红蛛</t>
+  </si>
+  <si>
+    <t>230000</t>
+  </si>
+  <si>
+    <t>节日魔龙</t>
   </si>
   <si>
     <t>300000</t>
   </si>
   <si>
-    <t>200000000</t>
-  </si>
-  <si>
-    <t>1012,2007</t>
-  </si>
-  <si>
-    <t>节日僵尸</t>
+    <t>节日雷龙</t>
+  </si>
+  <si>
+    <t>400000</t>
+  </si>
+  <si>
+    <t>节日冰龙</t>
   </si>
   <si>
     <t>600000</t>
   </si>
   <si>
-    <t>400000000</t>
-  </si>
-  <si>
-    <t>节日恶魔</t>
+    <t>节日月狐</t>
+  </si>
+  <si>
+    <t>800000</t>
+  </si>
+  <si>
+    <t>节日巨魔</t>
   </si>
   <si>
     <t>1000000</t>
   </si>
   <si>
-    <t>800000000</t>
-  </si>
-  <si>
-    <t>节日蜈蚣</t>
+    <t>卧龙小兵</t>
+  </si>
+  <si>
+    <t>1200000</t>
+  </si>
+  <si>
+    <t>节日蝙蝠</t>
+  </si>
+  <si>
+    <t>1400000</t>
+  </si>
+  <si>
+    <t>节日骨魔</t>
+  </si>
+  <si>
+    <t>1700000</t>
+  </si>
+  <si>
+    <t>节日金龙</t>
   </si>
   <si>
     <t>2000000</t>
-  </si>
-  <si>
-    <t>1600000000</t>
-  </si>
-  <si>
-    <t>1012,2007,1008</t>
-  </si>
-  <si>
-    <t>节日野猪</t>
-  </si>
-  <si>
-    <t>3000000</t>
-  </si>
-  <si>
-    <t>3000000000</t>
-  </si>
-  <si>
-    <t>节日邪魔</t>
-  </si>
-  <si>
-    <t>4000000</t>
-  </si>
-  <si>
-    <t>6000000000</t>
-  </si>
-  <si>
-    <t>节日红蛛</t>
-  </si>
-  <si>
-    <t>350000</t>
-  </si>
-  <si>
-    <t>600000000</t>
-  </si>
-  <si>
-    <t>节日魔龙</t>
-  </si>
-  <si>
-    <t>400000</t>
-  </si>
-  <si>
-    <t>700000000</t>
-  </si>
-  <si>
-    <t>节日雷龙</t>
-  </si>
-  <si>
-    <t>500000</t>
-  </si>
-  <si>
-    <t>750000000</t>
-  </si>
-  <si>
-    <t>节日冰龙</t>
-  </si>
-  <si>
-    <t>900000000</t>
-  </si>
-  <si>
-    <t>节日月狐</t>
-  </si>
-  <si>
-    <t>800000</t>
-  </si>
-  <si>
-    <t>1200000000</t>
-  </si>
-  <si>
-    <t>节日巨魔</t>
-  </si>
-  <si>
-    <t>1500000000</t>
-  </si>
-  <si>
-    <t>卧龙小兵</t>
-  </si>
-  <si>
-    <t>1300000</t>
-  </si>
-  <si>
-    <t>1950000000</t>
-  </si>
-  <si>
-    <t>节日蝙蝠</t>
-  </si>
-  <si>
-    <t>1600000</t>
-  </si>
-  <si>
-    <t>2400000000</t>
-  </si>
-  <si>
-    <t>节日骨魔</t>
   </si>
 </sst>
 </file>
@@ -443,13 +383,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -894,41 +834,31 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1248,242 +1178,194 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="4" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="17" style="6" customWidth="1"/>
-    <col min="7" max="8" width="19.25" style="6" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="4" customWidth="1"/>
-    <col min="12" max="12" width="12" style="4" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="33.9166666666667" style="4" customWidth="1"/>
-    <col min="15" max="16" width="9" style="4"/>
-    <col min="17" max="17" width="11.625" style="6" customWidth="1"/>
-    <col min="18" max="18" width="17" style="6" customWidth="1"/>
-    <col min="19" max="19" width="19.25" style="6" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="4"/>
+    <col min="5" max="5" width="11.625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17" style="5" customWidth="1"/>
+    <col min="7" max="8" width="19.25" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="12" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.375" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="Q1" s="7" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="Q1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="7" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="P2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="R2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="8" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="9" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="D4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="8" t="s">
+      <c r="H4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="9" t="s">
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:17">
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" ref="G6:G25" si="0">F6*P6*1000</f>
+        <v>1000000</v>
+      </c>
+      <c r="H6" s="10">
         <v>10</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="S4" s="10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="R5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S5" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:19">
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="11">
-        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
@@ -1500,37 +1382,32 @@
       <c r="M6" s="2">
         <v>99</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="14" t="s">
+      <c r="P6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="14" t="s">
+      <c r="F7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="S6" s="14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C7" s="5">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="11">
-        <f t="shared" ref="H7:H15" si="0">H6+20</f>
+      <c r="G7" s="10">
+        <f t="shared" si="0"/>
+        <v>20000000</v>
+      </c>
+      <c r="H7" s="10">
+        <f t="shared" ref="H7:H25" si="1">H6+10</f>
         <v>20</v>
       </c>
       <c r="I7" s="2">
@@ -1548,38 +1425,33 @@
       <c r="M7" s="2">
         <v>99</v>
       </c>
-      <c r="N7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="R7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C8" s="5">
+      <c r="P7" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C8" s="4">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="11">
+      <c r="D8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="10">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>60000000</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
       <c r="I8" s="2">
         <v>100</v>
@@ -1596,38 +1468,33 @@
       <c r="M8" s="2">
         <v>99</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="P8" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C9" s="4">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="R8" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="S8" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="11">
+      <c r="E9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="10">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>120000000</v>
+      </c>
+      <c r="H9" s="10">
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="I9" s="2">
         <v>100</v>
@@ -1644,38 +1511,33 @@
       <c r="M9" s="2">
         <v>99</v>
       </c>
-      <c r="N9" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="R9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S9" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C10" s="5">
+      <c r="P9" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C10" s="4">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="11">
+      <c r="D10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="10">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>200000000</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
       <c r="I10" s="2">
         <v>100</v>
@@ -1692,38 +1554,33 @@
       <c r="M10" s="2">
         <v>99</v>
       </c>
-      <c r="N10" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="S10" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C11" s="5">
+      <c r="P10" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C11" s="4">
         <v>6</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="11">
+      <c r="D11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>300000000</v>
+      </c>
+      <c r="H11" s="10">
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
       <c r="I11" s="2">
         <v>100</v>
@@ -1740,38 +1597,33 @@
       <c r="M11" s="2">
         <v>99</v>
       </c>
-      <c r="N11" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q11" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="R11" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="S11" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C12" s="5">
+      <c r="P11" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C12" s="4">
         <v>7</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="11">
+      <c r="D12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="10">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>490000000</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" si="1"/>
+        <v>70</v>
       </c>
       <c r="I12" s="2">
         <v>100</v>
@@ -1788,38 +1640,33 @@
       <c r="M12" s="2">
         <v>99</v>
       </c>
-      <c r="N12" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="R12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="S12" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C13" s="5">
+      <c r="P12" s="2">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C13" s="4">
         <v>8</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="11">
+      <c r="D13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="10">
         <f t="shared" si="0"/>
-        <v>140</v>
+        <v>720000000</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
       <c r="I13" s="2">
         <v>100</v>
@@ -1836,38 +1683,33 @@
       <c r="M13" s="2">
         <v>99</v>
       </c>
-      <c r="N13" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C14" s="5">
+      <c r="P13" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C14" s="4">
         <v>9</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="11">
+      <c r="D14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="10">
         <f t="shared" si="0"/>
-        <v>160</v>
+        <v>1170000000</v>
+      </c>
+      <c r="H14" s="10">
+        <f t="shared" si="1"/>
+        <v>90</v>
       </c>
       <c r="I14" s="2">
         <v>100</v>
@@ -1884,38 +1726,33 @@
       <c r="M14" s="2">
         <v>99</v>
       </c>
-      <c r="N14" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q14" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="R14" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="S14" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:19">
-      <c r="C15" s="5">
+      <c r="P14" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C15" s="4">
         <v>10</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="11">
+      <c r="D15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="10">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>1700000000</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="I15" s="2">
         <v>100</v>
@@ -1932,514 +1769,449 @@
       <c r="M15" s="2">
         <v>99</v>
       </c>
-      <c r="N15" s="15" t="s">
+      <c r="P15" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="C16" s="4">
+        <v>11</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="0"/>
+        <v>2530000000</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="I16" s="2">
+        <v>100</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M16" s="2">
+        <v>99</v>
+      </c>
+      <c r="P16" s="2">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C17" s="4">
+        <v>12</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="0"/>
+        <v>3600000000</v>
+      </c>
+      <c r="H17" s="10">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="I17" s="2">
+        <v>100</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M17" s="2">
+        <v>99</v>
+      </c>
+      <c r="P17" s="2">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C18" s="4">
+        <v>13</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" si="0"/>
+        <v>5200000000</v>
+      </c>
+      <c r="H18" s="10">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="I18" s="2">
+        <v>100</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M18" s="2">
+        <v>99</v>
+      </c>
+      <c r="P18" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C19" s="4">
+        <v>14</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="10">
+        <f t="shared" si="0"/>
+        <v>8400000000</v>
+      </c>
+      <c r="H19" s="10">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="I19" s="2">
+        <v>100</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M19" s="2">
+        <v>99</v>
+      </c>
+      <c r="P19" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C20" s="4">
+        <v>15</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="10">
+        <f t="shared" si="0"/>
+        <v>12000000000</v>
+      </c>
+      <c r="H20" s="10">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="I20" s="2">
+        <v>100</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L20" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M20" s="2">
+        <v>99</v>
+      </c>
+      <c r="P20" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C21" s="4">
+        <v>16</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="Q15" s="14" t="s">
+      <c r="E21" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" si="0"/>
+        <v>16000000000</v>
+      </c>
+      <c r="H21" s="10">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="I21" s="2">
+        <v>100</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M21" s="2">
+        <v>99</v>
+      </c>
+      <c r="P21" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C22" s="4">
+        <v>17</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="10">
+        <f t="shared" si="0"/>
+        <v>20400000000</v>
+      </c>
+      <c r="H22" s="10">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="I22" s="2">
+        <v>100</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M22" s="2">
+        <v>99</v>
+      </c>
+      <c r="P22" s="2">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C23" s="4">
+        <v>18</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="R15" s="14" t="s">
+      <c r="F23" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="14" t="s">
+      <c r="G23" s="10">
+        <f t="shared" si="0"/>
+        <v>25200000000</v>
+      </c>
+      <c r="H23" s="10">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="I23" s="2">
+        <v>100</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L23" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M23" s="2">
+        <v>99</v>
+      </c>
+      <c r="P23" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C24" s="4">
+        <v>19</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12">
-        <v>11</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="E24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="F24" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="10">
+        <f t="shared" si="0"/>
+        <v>32300000000</v>
+      </c>
+      <c r="H24" s="10">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="I24" s="2">
+        <v>100</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M24" s="2">
+        <v>99</v>
+      </c>
+      <c r="P24" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C25" s="4">
+        <v>20</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="16" t="s">
+      <c r="E25" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="13">
-        <f t="shared" ref="H7:H24" si="1">H15+10</f>
-        <v>190</v>
-      </c>
-      <c r="I16" s="3">
-        <v>100</v>
-      </c>
-      <c r="J16" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K16" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L16" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M16" s="3">
-        <v>99</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q16" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="S16" s="16" t="s">
+      <c r="F25" s="11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A17" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="12">
-        <v>12</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="13">
+      <c r="G25" s="10">
+        <f t="shared" si="0"/>
+        <v>40000000000</v>
+      </c>
+      <c r="H25" s="10">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I25" s="2">
         <v>100</v>
       </c>
-      <c r="J17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="J25" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M25" s="2">
         <v>99</v>
       </c>
-      <c r="N17" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q17" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="R17" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="S17" s="16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="12">
-        <v>13</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="H18" s="13">
-        <f t="shared" si="1"/>
-        <v>210</v>
-      </c>
-      <c r="I18" s="3">
-        <v>100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>99</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="R18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="S18" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="12">
-        <v>14</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="13">
-        <f t="shared" si="1"/>
-        <v>220</v>
-      </c>
-      <c r="I19" s="3">
-        <v>100</v>
-      </c>
-      <c r="J19" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K19" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L19" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M19" s="3">
-        <v>99</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q19" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="R19" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="S19" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="12">
-        <v>15</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="13">
-        <f t="shared" si="1"/>
-        <v>230</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M20" s="3">
-        <v>99</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q20" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="R20" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="S20" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="12">
-        <v>16</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21" s="13">
-        <f t="shared" si="1"/>
-        <v>240</v>
-      </c>
-      <c r="I21" s="3">
-        <v>100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>99</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q21" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="R21" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="S21" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A22" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12">
-        <v>17</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H22" s="13">
-        <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>99</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q22" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="R22" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="S22" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A23" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="12">
-        <v>18</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="13">
-        <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-      <c r="I23" s="3">
-        <v>100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M23" s="3">
-        <v>99</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q23" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="R23" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="S23" s="16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A24" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="12">
-        <v>19</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H24" s="13">
-        <f t="shared" si="1"/>
-        <v>270</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M24" s="3">
-        <v>99</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q24" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="R24" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="S24" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="5:19">
-      <c r="E25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="S25" s="11"/>
+      <c r="P25" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:17">
+      <c r="E26" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5 Q3:S5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5 H3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterFestiveConfig.xlsx
+++ b/Excel/MonsterFestiveConfig.xlsx
@@ -188,13 +188,13 @@
     <t>节日骨魔</t>
   </si>
   <si>
-    <t>1700000</t>
+    <t>1600000</t>
   </si>
   <si>
     <t>节日金龙</t>
   </si>
   <si>
-    <t>2000000</t>
+    <t>1800000</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="G24" s="10">
         <f t="shared" si="0"/>
-        <v>32300000000</v>
+        <v>30400000000</v>
       </c>
       <c r="H24" s="10">
         <f t="shared" si="1"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="G25" s="10">
         <f t="shared" si="0"/>
-        <v>40000000000</v>
+        <v>36000000000</v>
       </c>
       <c r="H25" s="10">
         <f t="shared" si="1"/>
@@ -2211,7 +2211,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5 H3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterFestiveConfig.xlsx
+++ b/Excel/MonsterFestiveConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
   <si>
     <t>#</t>
   </si>
@@ -195,6 +195,36 @@
   </si>
   <si>
     <t>1800000</t>
+  </si>
+  <si>
+    <t>3600000</t>
+  </si>
+  <si>
+    <t>7200000</t>
+  </si>
+  <si>
+    <t>15000000</t>
+  </si>
+  <si>
+    <t>30000000</t>
+  </si>
+  <si>
+    <t>60000000</t>
+  </si>
+  <si>
+    <t>120000000</t>
+  </si>
+  <si>
+    <t>240000000</t>
+  </si>
+  <si>
+    <t>480000000</t>
+  </si>
+  <si>
+    <t>1000000000</t>
+  </si>
+  <si>
+    <t>2000000000</t>
   </si>
 </sst>
 </file>
@@ -374,12 +404,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -710,7 +746,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -734,16 +770,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -752,111 +788,119 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1178,37 +1222,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="5" customWidth="1"/>
     <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="17" style="5" customWidth="1"/>
-    <col min="7" max="8" width="19.25" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="12" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.375" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="3"/>
+    <col min="5" max="5" width="11.625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="17" style="6" customWidth="1"/>
+    <col min="7" max="8" width="19.25" style="6" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="12" style="4" customWidth="1"/>
+    <col min="13" max="13" width="9.375" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
       <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1217,18 +1261,18 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
       <c r="P2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1237,134 +1281,134 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="7" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="7" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:17">
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="10">
-        <f t="shared" ref="G6:G25" si="0">F6*P6*1000</f>
+      <c r="G6" s="11">
+        <f t="shared" ref="G6:G26" si="0">F6*P6*1000</f>
         <v>1000000</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="11">
         <v>10</v>
       </c>
       <c r="I6" s="2">
@@ -1385,29 +1429,29 @@
       <c r="P6" s="2">
         <v>1</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="4">
         <v>1000</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="11">
         <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
-      <c r="H7" s="10">
-        <f t="shared" ref="H7:H25" si="1">H6+10</f>
+      <c r="H7" s="11">
+        <f t="shared" ref="H7:H35" si="1">H6+10</f>
         <v>20</v>
       </c>
       <c r="I7" s="2">
@@ -1428,28 +1472,28 @@
       <c r="P7" s="2">
         <v>2</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="4">
         <v>2000</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="11">
         <f t="shared" si="0"/>
         <v>60000000</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -1471,28 +1515,28 @@
       <c r="P8" s="2">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="4">
         <v>3000</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="11">
         <f t="shared" si="0"/>
         <v>120000000</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="11">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
@@ -1514,28 +1558,28 @@
       <c r="P9" s="2">
         <v>4</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="4">
         <v>4000</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>5</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="11">
         <f t="shared" si="0"/>
         <v>200000000</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="11">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
@@ -1557,28 +1601,28 @@
       <c r="P10" s="2">
         <v>5</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="4">
         <v>5000</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>6</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="11">
         <f t="shared" si="0"/>
         <v>300000000</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="11">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
@@ -1600,28 +1644,28 @@
       <c r="P11" s="2">
         <v>6</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="4">
         <v>5000</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>7</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="11">
         <f t="shared" si="0"/>
         <v>490000000</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="11">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
@@ -1643,28 +1687,28 @@
       <c r="P12" s="2">
         <v>7</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="4">
         <v>6000</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>8</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="11">
         <f t="shared" si="0"/>
         <v>720000000</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="11">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
@@ -1686,28 +1730,28 @@
       <c r="P13" s="2">
         <v>8</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="4">
         <v>6000</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>9</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="11">
         <f t="shared" si="0"/>
         <v>1170000000</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="11">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
@@ -1729,28 +1773,28 @@
       <c r="P14" s="2">
         <v>9</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="4">
         <v>7000</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>10</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="11">
         <f t="shared" si="0"/>
         <v>1700000000</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="11">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -1772,28 +1816,28 @@
       <c r="P15" s="2">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="4">
         <v>7000</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:17">
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>11</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="11">
         <f t="shared" si="0"/>
         <v>2530000000</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="11">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
@@ -1815,28 +1859,28 @@
       <c r="P16" s="2">
         <v>11</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="Q16" s="4">
         <v>8000</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>12</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="11">
         <f t="shared" si="0"/>
         <v>3600000000</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="11">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
@@ -1858,28 +1902,28 @@
       <c r="P17" s="2">
         <v>12</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="4">
         <v>8000</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>13</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="11">
         <f t="shared" si="0"/>
         <v>5200000000</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="11">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
@@ -1901,28 +1945,28 @@
       <c r="P18" s="2">
         <v>13</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="4">
         <v>9000</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>14</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="11">
         <f t="shared" si="0"/>
         <v>8400000000</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="11">
         <f t="shared" si="1"/>
         <v>140</v>
       </c>
@@ -1944,28 +1988,28 @@
       <c r="P19" s="2">
         <v>14</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="Q19" s="4">
         <v>9000</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>15</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="11">
         <f t="shared" si="0"/>
         <v>12000000000</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="11">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
@@ -1987,28 +2031,28 @@
       <c r="P20" s="2">
         <v>15</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="4">
         <v>10000</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>16</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="11">
         <f t="shared" si="0"/>
         <v>16000000000</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="11">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
@@ -2030,28 +2074,28 @@
       <c r="P21" s="2">
         <v>16</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="4">
         <v>10000</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>17</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="11">
         <f t="shared" si="0"/>
         <v>20400000000</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="11">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
@@ -2078,23 +2122,23 @@
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>18</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="11">
         <f t="shared" si="0"/>
         <v>25200000000</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="11">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
@@ -2121,23 +2165,23 @@
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <v>19</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="11">
         <f t="shared" si="0"/>
         <v>30400000000</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="11">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
@@ -2159,28 +2203,28 @@
       <c r="P24" s="2">
         <v>19</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="4">
         <v>12000</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>20</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="11">
         <f t="shared" si="0"/>
         <v>36000000000</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="11">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -2202,12 +2246,464 @@
       <c r="P25" s="2">
         <v>20</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="Q25" s="4">
         <v>15000</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:17">
-      <c r="E26" s="10"/>
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C26" s="12">
+        <v>21</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="13">
+        <f>F26*P26*2000</f>
+        <v>79200000000</v>
+      </c>
+      <c r="H26" s="11">
+        <f t="shared" ref="H26:H35" si="2">H25+20</f>
+        <v>220</v>
+      </c>
+      <c r="I26" s="3">
+        <v>100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M26" s="3">
+        <v>99</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:17">
+      <c r="C27" s="5">
+        <v>22</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="11">
+        <f>F27*P27*2100</f>
+        <v>181440000000</v>
+      </c>
+      <c r="H27" s="11">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="I27" s="2">
+        <v>100</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L27" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M27" s="2">
+        <v>99</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2">
+        <v>12</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:17">
+      <c r="C28" s="5">
+        <v>23</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="11">
+        <f>F28*P28*2200</f>
+        <v>429000000000</v>
+      </c>
+      <c r="H28" s="11">
+        <f t="shared" si="2"/>
+        <v>260</v>
+      </c>
+      <c r="I28" s="2">
+        <v>100</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L28" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M28" s="2">
+        <v>99</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:17">
+      <c r="C29" s="5">
+        <v>24</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" s="11">
+        <f>F29*P29*2300</f>
+        <v>966000000000</v>
+      </c>
+      <c r="H29" s="11">
+        <f t="shared" si="2"/>
+        <v>280</v>
+      </c>
+      <c r="I29" s="2">
+        <v>100</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L29" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M29" s="2">
+        <v>99</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:17">
+      <c r="C30" s="5">
+        <v>25</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="11">
+        <f>F30*P30*2200</f>
+        <v>1980000000000</v>
+      </c>
+      <c r="H30" s="11">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="I30" s="2">
+        <v>100</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L30" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M30" s="2">
+        <v>99</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:17">
+      <c r="C31" s="5">
+        <v>26</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="11">
+        <f>F31*P31*2400</f>
+        <v>4608000000000</v>
+      </c>
+      <c r="H31" s="11">
+        <f t="shared" si="2"/>
+        <v>320</v>
+      </c>
+      <c r="I31" s="2">
+        <v>100</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L31" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M31" s="2">
+        <v>99</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:17">
+      <c r="C32" s="5">
+        <v>27</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="11">
+        <f>F32*P32*2200</f>
+        <v>8976000000000</v>
+      </c>
+      <c r="H32" s="11">
+        <f t="shared" si="2"/>
+        <v>340</v>
+      </c>
+      <c r="I32" s="2">
+        <v>100</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L32" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M32" s="2">
+        <v>99</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2">
+        <v>17</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:17">
+      <c r="C33" s="5">
+        <v>28</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33" s="11">
+        <f>F33*P33*2500</f>
+        <v>21600000000000</v>
+      </c>
+      <c r="H33" s="11">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+      <c r="I33" s="2">
+        <v>100</v>
+      </c>
+      <c r="J33" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L33" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M33" s="2">
+        <v>99</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:17">
+      <c r="C34" s="5">
+        <v>29</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G34" s="11">
+        <f>F34*P34*2600</f>
+        <v>49400000000000</v>
+      </c>
+      <c r="H34" s="11">
+        <f t="shared" si="2"/>
+        <v>380</v>
+      </c>
+      <c r="I34" s="2">
+        <v>100</v>
+      </c>
+      <c r="J34" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L34" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M34" s="2">
+        <v>99</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:17">
+      <c r="C35" s="5">
+        <v>30</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="11">
+        <f>F35*P35*2700</f>
+        <v>108000000000000</v>
+      </c>
+      <c r="H35" s="11">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="I35" s="2">
+        <v>100</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1800</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1800</v>
+      </c>
+      <c r="L35" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M35" s="2">
+        <v>99</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:17">
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/MonsterFestiveConfig.xlsx
+++ b/Excel/MonsterFestiveConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -197,34 +197,64 @@
     <t>1800000</t>
   </si>
   <si>
-    <t>3600000</t>
-  </si>
-  <si>
-    <t>7200000</t>
-  </si>
-  <si>
-    <t>15000000</t>
-  </si>
-  <si>
-    <t>30000000</t>
-  </si>
-  <si>
-    <t>60000000</t>
-  </si>
-  <si>
-    <t>120000000</t>
-  </si>
-  <si>
-    <t>240000000</t>
-  </si>
-  <si>
-    <t>480000000</t>
-  </si>
-  <si>
-    <t>1000000000</t>
-  </si>
-  <si>
-    <t>2000000000</t>
+    <t>节日木龙</t>
+  </si>
+  <si>
+    <t>3200000</t>
+  </si>
+  <si>
+    <t>节日水龙</t>
+  </si>
+  <si>
+    <t>5000000</t>
+  </si>
+  <si>
+    <t>节日火龙</t>
+  </si>
+  <si>
+    <t>7000000</t>
+  </si>
+  <si>
+    <t>节日土龙</t>
+  </si>
+  <si>
+    <t>10000000</t>
+  </si>
+  <si>
+    <t>节日仙鸡</t>
+  </si>
+  <si>
+    <t>20000000</t>
+  </si>
+  <si>
+    <t>节日仙鹿</t>
+  </si>
+  <si>
+    <t>40000000</t>
+  </si>
+  <si>
+    <t>节日仙魂</t>
+  </si>
+  <si>
+    <t>70000000</t>
+  </si>
+  <si>
+    <t>节日仙蛟</t>
+  </si>
+  <si>
+    <t>100000000</t>
+  </si>
+  <si>
+    <t>节日仙虫</t>
+  </si>
+  <si>
+    <t>150000000</t>
+  </si>
+  <si>
+    <t>节日仙鸾</t>
+  </si>
+  <si>
+    <t>200000000</t>
   </si>
 </sst>
 </file>
@@ -2255,17 +2285,17 @@
         <v>21</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G26" s="13">
         <f>F26*P26*2000</f>
-        <v>79200000000</v>
+        <v>134400000000</v>
       </c>
       <c r="H26" s="11">
         <f t="shared" ref="H26:H35" si="2">H25+20</f>
@@ -2288,8 +2318,8 @@
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
-      <c r="P26" s="3">
-        <v>11</v>
+      <c r="P26" s="2">
+        <v>21</v>
       </c>
       <c r="Q26" s="3">
         <v>8000</v>
@@ -2300,17 +2330,17 @@
         <v>22</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G27" s="11">
         <f>F27*P27*2100</f>
-        <v>181440000000</v>
+        <v>231000000000</v>
       </c>
       <c r="H27" s="11">
         <f t="shared" si="2"/>
@@ -2334,7 +2364,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q27" s="4">
         <v>8000</v>
@@ -2345,17 +2375,17 @@
         <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G28" s="11">
         <f>F28*P28*2200</f>
-        <v>429000000000</v>
+        <v>354200000000</v>
       </c>
       <c r="H28" s="11">
         <f t="shared" si="2"/>
@@ -2379,7 +2409,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Q28" s="4">
         <v>9000</v>
@@ -2390,17 +2420,17 @@
         <v>24</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G29" s="11">
         <f>F29*P29*2300</f>
-        <v>966000000000</v>
+        <v>552000000000</v>
       </c>
       <c r="H29" s="11">
         <f t="shared" si="2"/>
@@ -2424,7 +2454,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Q29" s="4">
         <v>9000</v>
@@ -2435,17 +2465,17 @@
         <v>25</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G30" s="11">
         <f>F30*P30*2200</f>
-        <v>1980000000000</v>
+        <v>1100000000000</v>
       </c>
       <c r="H30" s="11">
         <f t="shared" si="2"/>
@@ -2469,7 +2499,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q30" s="4">
         <v>10000</v>
@@ -2480,17 +2510,17 @@
         <v>26</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G31" s="11">
         <f>F31*P31*2400</f>
-        <v>4608000000000</v>
+        <v>2496000000000</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="2"/>
@@ -2514,7 +2544,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Q31" s="4">
         <v>10000</v>
@@ -2525,17 +2555,17 @@
         <v>27</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G32" s="11">
         <f>F32*P32*2200</f>
-        <v>8976000000000</v>
+        <v>4158000000000</v>
       </c>
       <c r="H32" s="11">
         <f t="shared" si="2"/>
@@ -2559,7 +2589,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="Q32" s="2">
         <v>11000</v>
@@ -2570,17 +2600,17 @@
         <v>28</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G33" s="11">
         <f>F33*P33*2500</f>
-        <v>21600000000000</v>
+        <v>7000000000000</v>
       </c>
       <c r="H33" s="11">
         <f t="shared" si="2"/>
@@ -2604,7 +2634,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Q33" s="2">
         <v>11000</v>
@@ -2615,17 +2645,17 @@
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G34" s="11">
         <f>F34*P34*2600</f>
-        <v>49400000000000</v>
+        <v>11310000000000</v>
       </c>
       <c r="H34" s="11">
         <f t="shared" si="2"/>
@@ -2649,7 +2679,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Q34" s="4">
         <v>12000</v>
@@ -2660,17 +2690,17 @@
         <v>30</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G35" s="11">
         <f>F35*P35*2700</f>
-        <v>108000000000000</v>
+        <v>16200000000000</v>
       </c>
       <c r="H35" s="11">
         <f t="shared" si="2"/>
@@ -2694,7 +2724,7 @@
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Q35" s="4">
         <v>15000</v>
